--- a/risk_matrix/risk_matrix_2026.xlsx
+++ b/risk_matrix/risk_matrix_2026.xlsx
@@ -502,7 +502,9 @@
       </c>
       <c r="B2" s="3" t="inlineStr"/>
       <c r="C2" s="3" t="inlineStr"/>
-      <c r="D2" s="3" t="inlineStr"/>
+      <c r="D2" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="E2" s="3" t="inlineStr"/>
       <c r="F2" s="3" t="inlineStr"/>
       <c r="G2" s="3" t="inlineStr"/>
@@ -517,10 +519,10 @@
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr"/>
       <c r="E3" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
     </row>
@@ -531,14 +533,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr"/>
-      <c r="C4" s="3" t="inlineStr"/>
-      <c r="D4" s="3" t="inlineStr"/>
-      <c r="E4" s="4" t="n">
+      <c r="C4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F4" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="E4" s="3" t="inlineStr"/>
+      <c r="F4" s="3" t="inlineStr"/>
       <c r="G4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
@@ -577,7 +579,7 @@
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="3" t="inlineStr"/>
       <c r="G7" s="3" t="inlineStr"/>

--- a/risk_matrix/risk_matrix_2026.xlsx
+++ b/risk_matrix/risk_matrix_2026.xlsx
@@ -502,10 +502,10 @@
       </c>
       <c r="B2" s="3" t="inlineStr"/>
       <c r="C2" s="3" t="inlineStr"/>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="3" t="inlineStr"/>
+      <c r="E2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="3" t="inlineStr"/>
       <c r="F2" s="3" t="inlineStr"/>
       <c r="G2" s="3" t="inlineStr"/>
     </row>
@@ -533,13 +533,13 @@
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr"/>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="3" t="inlineStr"/>
+      <c r="D4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="E4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E4" s="3" t="inlineStr"/>
       <c r="F4" s="3" t="inlineStr"/>
       <c r="G4" s="3" t="inlineStr"/>
     </row>
@@ -563,10 +563,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr"/>
-      <c r="C6" s="3" t="inlineStr"/>
+      <c r="C6" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="D6" s="3" t="inlineStr"/>
       <c r="E6" s="3" t="inlineStr"/>
-      <c r="F6" s="3" t="inlineStr"/>
+      <c r="F6" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="G6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
@@ -579,9 +583,11 @@
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="G7" s="3" t="inlineStr"/>
     </row>
   </sheetData>

--- a/risk_matrix/risk_matrix_2026.xlsx
+++ b/risk_matrix/risk_matrix_2026.xlsx
@@ -503,9 +503,7 @@
       <c r="B2" s="3" t="inlineStr"/>
       <c r="C2" s="3" t="inlineStr"/>
       <c r="D2" s="3" t="inlineStr"/>
-      <c r="E2" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="E2" s="3" t="inlineStr"/>
       <c r="F2" s="3" t="inlineStr"/>
       <c r="G2" s="3" t="inlineStr"/>
     </row>
@@ -519,10 +517,10 @@
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr"/>
       <c r="E3" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
     </row>
@@ -535,7 +533,7 @@
       <c r="B4" s="3" t="inlineStr"/>
       <c r="C4" s="3" t="inlineStr"/>
       <c r="D4" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>2</v>
@@ -562,15 +560,17 @@
           <t>Low-level malicious attack</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr"/>
+      <c r="B6" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="C6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="3" t="inlineStr"/>
+      <c r="D6" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="E6" s="3" t="inlineStr"/>
-      <c r="F6" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" s="3" t="inlineStr"/>
     </row>
     <row r="7">

--- a/risk_matrix/risk_matrix_2026.xlsx
+++ b/risk_matrix/risk_matrix_2026.xlsx
@@ -517,10 +517,10 @@
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr"/>
       <c r="E3" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
     </row>
@@ -531,14 +531,18 @@
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr"/>
-      <c r="C4" s="3" t="inlineStr"/>
+      <c r="C4" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="D4" s="4" t="n">
         <v>2</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" s="3" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="G4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
@@ -569,7 +573,9 @@
       <c r="D6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="3" t="inlineStr"/>
+      <c r="E6" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" s="3" t="inlineStr"/>
     </row>
@@ -580,10 +586,14 @@
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="3" t="inlineStr"/>
+      <c r="C7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="E7" s="4" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F7" s="4" t="n">
         <v>1</v>

--- a/risk_matrix/risk_matrix_2026.xlsx
+++ b/risk_matrix/risk_matrix_2026.xlsx
@@ -517,10 +517,10 @@
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr"/>
       <c r="E3" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
     </row>
@@ -593,7 +593,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F7" s="4" t="n">
         <v>1</v>

--- a/risk_matrix/risk_matrix_2026.xlsx
+++ b/risk_matrix/risk_matrix_2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Risk Matrix" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Matrix" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,11 +27,11 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -68,10 +68,10 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -504,7 +504,9 @@
       <c r="C2" s="3" t="inlineStr"/>
       <c r="D2" s="3" t="inlineStr"/>
       <c r="E2" s="3" t="inlineStr"/>
-      <c r="F2" s="3" t="inlineStr"/>
+      <c r="F2" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="G2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
@@ -513,14 +515,18 @@
           <t>Extensive compromise</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr"/>
+      <c r="B3" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
+      <c r="D3" s="4" t="n">
+        <v>3</v>
+      </c>
       <c r="E3" s="4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
     </row>
@@ -530,19 +536,19 @@
           <t>Isolated compromise</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr"/>
+      <c r="B4" s="4" t="n">
+        <v>3</v>
+      </c>
       <c r="C4" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="F4" s="3" t="inlineStr"/>
       <c r="G4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
@@ -568,15 +574,17 @@
         <v>1</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="3" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="G6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
@@ -586,17 +594,15 @@
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
     </row>
